--- a/Assets/02Script/Table/ItemTable.xlsx
+++ b/Assets/02Script/Table/ItemTable.xlsx
@@ -93,7 +93,7 @@
     <t>&lt;i&gt;열리지 않는&lt;/i&gt; 이상한 양동이다.</t>
   </si>
   <si>
-    <t>Dialog</t>
+    <t>Narrative</t>
   </si>
   <si>
     <t>Reply</t>
@@ -119,6 +119,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$₩-412]#,##0.00"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="10.0"/>
@@ -150,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -165,6 +168,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,7 +628,7 @@
       <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>30</v>
       </c>
       <c r="F2" s="1" t="s">

--- a/Assets/02Script/Table/ItemTable.xlsx
+++ b/Assets/02Script/Table/ItemTable.xlsx
@@ -7,6 +7,7 @@
     <sheet state="visible" name="Interactable" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Inspectable" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Readable" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Special" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="67">
   <si>
     <t>ItemID</t>
   </si>
@@ -53,6 +54,41 @@
   </si>
   <si>
     <t>Icons_1</t>
+  </si>
+  <si>
+    <t>첫 번째 열쇠</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;첫 번째 열쇠&lt;/color&gt;. 베일리라는 하녀가 보관했던 열쇠다.</t>
+  </si>
+  <si>
+    <t>Icons_2</t>
+  </si>
+  <si>
+    <t>지포 라이터</t>
+  </si>
+  <si>
+    <t>고급스럽게 생긴 &lt;b&gt;지포 라이터&lt;/b&gt;다.
+&lt;i&gt;불을 사용할 데가 있을까?&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>Icons_3</t>
+  </si>
+  <si>
+    <t>두 번째 열쇠</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;두 번째 열쇠&lt;/color&gt;. 어디에 써야 할지는 자명하다.</t>
+  </si>
+  <si>
+    <t>주머니 칼</t>
+  </si>
+  <si>
+    <t>사용감이 많은 작은 칼.
+쓸 데가 어딘가엔 있겠지?</t>
+  </si>
+  <si>
+    <t>Icons_4</t>
   </si>
   <si>
     <t>Monologue</t>
@@ -84,6 +120,28 @@
 &lt;i&gt;혼자 놀고있는 책을 어디서 본 것 같은데...&lt;/i&gt;</t>
   </si>
   <si>
+    <t>첫번째 자물쇠</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;첫 번째&lt;/color&gt; 자물쇠.
+이 문 너머를 조사해보자.</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;첫 번째&lt;/color&gt; 자물쇠.
+&lt;i&gt;자물쇠라... 열쇠를 어디서 본 것 같기도?&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>촛불</t>
+  </si>
+  <si>
+    <t>왜인지 모르게 온기가 남아있는 것 같은 촛불이다.
+&lt;i&gt;촛불을 일렬로 나열해놓은 것이 특이하군.&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>일렬로 나열된 촛불이다.
+&lt;i&gt;어떤 촛불은 녹아 키가 작고, 어떤 촛불은 비교적 새거 같군.. 이게 힌트일까?&lt;/i&gt;</t>
+  </si>
+  <si>
     <t>낡은 양동이</t>
   </si>
   <si>
@@ -91,6 +149,27 @@
   </si>
   <si>
     <t>&lt;i&gt;열리지 않는&lt;/i&gt; 이상한 양동이다.</t>
+  </si>
+  <si>
+    <t>먼지쌓인 가족사진</t>
+  </si>
+  <si>
+    <t>행복해보이는 가족사진이다.
+먼지가 가득 쌓인 걸 보니 오랫동안 관리가 안된 듯 하다.</t>
+  </si>
+  <si>
+    <t>작은 메모지</t>
+  </si>
+  <si>
+    <t>메모가 적혀있다. 
+&lt;b&gt;무지개&lt;/b&gt;가 뜬 하늘 아래, &lt;i&gt;시간이 지나도 바래지 않는 것&lt;/i&gt;들만 남기고 모두 타서 사라지리라.</t>
+  </si>
+  <si>
+    <t>피묻은 정물화</t>
+  </si>
+  <si>
+    <t>피가 묻어있는 정물화다. 작은 메모가 붙어있다.
+&lt;i&gt;정물화에 관한 메모지일까? 자세히 볼 필요가 있겠다.&lt;/i&gt;</t>
   </si>
   <si>
     <t>Narrative</t>
@@ -113,6 +192,62 @@
   </si>
   <si>
     <t>&lt;i&gt;쓸데없이 긴글 같다...&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>베일리의 편지</t>
+  </si>
+  <si>
+    <t>콘솔 테이블 위에 놓인 &lt;b&gt;편지&lt;/b&gt;다. 종이가 많이 바래졌다.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;아가씨께.&lt;/b&gt;
+아가씨. 저택의 모든 사용인들이 떠났어요.
+&lt;b&gt;사라진 아가씨&lt;/b&gt;와, &lt;b&gt;미쳐버린 주인님&lt;/b&gt;, 고립된 저택 ...
+그렇게 모두 하나둘씩 떠나고, 저만 남았어요.
+혹시 아가씨께서 돌아오시지 않을까 기다렸지만.. 이제 한계예요.
+이곳엔 사람도, 온기도, 먹을 것도, 그 무엇도 존재하지않는 &lt;b&gt;유령 저택&lt;/b&gt;이 되었어요.
+아가씨를 이해하지만... 한편으로는 원망스럽습니다.
+혹시나 돌아올 아가씨를 위해, 제가 지녔던 열쇠를 서랍 안에 두고 갈게요.
+부디... 행복하세요, 아가씨.
+                    &lt;b&gt;하녀 베일리가.&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>꽤 오래된 편지 같은데. &lt;b&gt;사라진 아가씨와 유령 저택&lt;/b&gt;이라.. 흥미롭군.
+&lt;i&gt;그나저나 서랍에 열쇠가 있다고?&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>베일리의 일기</t>
+  </si>
+  <si>
+    <t>누군가의 &lt;b&gt;일기&lt;/b&gt;처럼 보인다.
+흠... 몰래 한번 읽어볼까?</t>
+  </si>
+  <si>
+    <t>예쁜 아가씨가 태어났다. 저택은 한 달째 축제가 벌어진 것만 같다.
+부인의 몸이 조금 편찮지만, 그래도 저택의 모두가 아가씨의 탄생을 축하하고 있다.
+주인님 두 분들은 아가씨를 너무나 아끼고, 사용인인 우리들 역시 예외는 없다.
+삭막했던 저택에 봄이 온 것 같다.
+사용인들은 아가씨의 생일인 &lt;b&gt;6월 15일&lt;/b&gt;을 기념일로 정해야 한다고 한입을 모아 얘기한다.
+아가씨가 쑥쑥 크셔서 말을 알아들을 수 있는 나이가 되시면 말해드려야지!
+&lt;i&gt;" 아가씨는 우리의 &lt;b&gt;축복&lt;/b&gt;이예요! 그리고, &lt;b&gt;축복&lt;/b&gt;의 시간이 되면, 우리 &lt;b&gt;축복&lt;/b&gt;의 아래, 선물과 함께 앞으로 나아갈 수 있는 길이 나타날 거예요. "&lt;/i&gt;
+             XX년 X월 하녀 베일리의 일기.</t>
+  </si>
+  <si>
+    <t>화목했던 것만 같은 저택인데..
+대체 무슨 일이 있었던 걸까?</t>
+  </si>
+  <si>
+    <t>EventType</t>
+  </si>
+  <si>
+    <t>조작가능한 시계</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>멈춰버린 시계다.
+&lt;i&gt;어디선가 &lt;b&gt;시간&lt;/b&gt;에 대한 힌트가 있던 것 같은데...&lt;/i&gt;</t>
   </si>
 </sst>
 </file>
@@ -193,6 +328,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -436,8 +575,8 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2">
-        <v>100.0</v>
+      <c r="F2" s="4">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +596,87 @@
         <v>12</v>
       </c>
       <c r="F3" s="4">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>1.0001003E7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>1.0001004E7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1">
         <v>101.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>1.0001005E7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1">
+        <v>102.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1.0001006E7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1">
+        <v>103.0</v>
       </c>
     </row>
   </sheetData>
@@ -487,10 +706,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -501,19 +720,19 @@
         <v>2.0001001E7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F2" s="1">
-        <v>100.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="3">
@@ -521,18 +740,58 @@
         <v>2.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>2.0001003E7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>2.0001004E7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="1">
         <v>101.0</v>
       </c>
     </row>
@@ -548,7 +807,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="29.63"/>
+    <col customWidth="1" min="4" max="4" width="42.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -562,7 +821,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
@@ -570,13 +829,55 @@
         <v>3.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>3.0001002E7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3.0001003E7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>3.0001004E7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +893,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="4" max="4" width="33.63"/>
-    <col customWidth="1" min="5" max="5" width="38.63"/>
+    <col customWidth="1" min="5" max="5" width="64.0"/>
+    <col customWidth="1" min="6" max="6" width="29.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,13 +908,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
@@ -620,19 +922,108 @@
         <v>4.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>4.0001002E7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>4.0001003E7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="40.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>5.0001001E7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02Script/Table/ItemTable.xlsx
+++ b/Assets/02Script/Table/ItemTable.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
   <si>
     <t>ItemID</t>
   </si>
@@ -81,14 +81,23 @@
     <t>&lt;color=blue&gt;두 번째 열쇠&lt;/color&gt;. 어디에 써야 할지는 자명하다.</t>
   </si>
   <si>
-    <t>주머니 칼</t>
-  </si>
-  <si>
-    <t>사용감이 많은 작은 칼.
-쓸 데가 어딘가엔 있겠지?</t>
+    <t>펜</t>
+  </si>
+  <si>
+    <t>탐정으로서 항상 몸에 지니는 펜이다.
+어딘가 쓸 데가 있으려나.</t>
   </si>
   <si>
     <t>Icons_4</t>
+  </si>
+  <si>
+    <t>쇠지렛대</t>
+  </si>
+  <si>
+    <t>튼튼해보이는 &lt;b&gt;쇠지렛대&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t>Icons_5</t>
   </si>
   <si>
     <t>Monologue</t>
@@ -142,6 +151,17 @@
 &lt;i&gt;어떤 촛불은 녹아 키가 작고, 어떤 촛불은 비교적 새거 같군.. 이게 힌트일까?&lt;/i&gt;</t>
   </si>
   <si>
+    <t>녹슨 상자</t>
+  </si>
+  <si>
+    <t>뭔가 들어있을 것 같은 &lt;b&gt;열리지 않는 상자&lt;/b&gt;다.
+특별히 잠금장치는 안 보이지만 녹슬어 꿈쩍도 않는다.</t>
+  </si>
+  <si>
+    <t>아무리 힘을 줘도 열리지 않는다.
+&lt;b&gt;도구&lt;/b&gt;가 필요할 것 같다.</t>
+  </si>
+  <si>
     <t>낡은 양동이</t>
   </si>
   <si>
@@ -162,14 +182,28 @@
   </si>
   <si>
     <t>메모가 적혀있다. 
-&lt;b&gt;무지개&lt;/b&gt;가 뜬 하늘 아래, &lt;i&gt;시간이 지나도 바래지 않는 것&lt;/i&gt;들만 남기고 모두 타서 사라지리라.</t>
+" &lt;b&gt;무지개&lt;/b&gt;가 뜬 하늘 아래, &lt;i&gt;시간이 지나도 바래지 않는 것&lt;/i&gt;들만 남기고 모두 타서 사라지리라. "</t>
   </si>
   <si>
     <t>피묻은 정물화</t>
   </si>
   <si>
-    <t>피가 묻어있는 정물화다. 작은 메모가 붙어있다.
+    <t>피가 묻어있는 정물화. 작은 메모가 붙어있다.
 &lt;i&gt;정물화에 관한 메모지일까? 자세히 볼 필요가 있겠다.&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>침대에 놓인 인형</t>
+  </si>
+  <si>
+    <t>아무것도 없는 유아용 침대에 덩그러니 놓인 인형이다.
+먼지가 많이 쌓여있다.</t>
+  </si>
+  <si>
+    <t>침대 서랍 속 인형</t>
+  </si>
+  <si>
+    <t>직접 만든 인형인가. 오래되어 그런지 색이 많이 바랬다.
+&lt;i&gt;그래도 이건 조금 으스스하게 생기지 않았나...?&lt;/i&gt;</t>
   </si>
   <si>
     <t>Narrative</t>
@@ -679,6 +713,26 @@
         <v>103.0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>1.0001007E7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1">
+        <v>104.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -706,10 +760,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -720,16 +774,16 @@
         <v>2.0001001E7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1">
         <v>-1.0</v>
@@ -740,16 +794,16 @@
         <v>2.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F3" s="1">
         <v>-1.0</v>
@@ -760,16 +814,16 @@
         <v>2.0001003E7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F4" s="1">
         <v>100.0</v>
@@ -780,19 +834,39 @@
         <v>2.0001004E7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1">
         <v>101.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>2.0001005E7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="1">
+        <v>104.0</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +895,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -829,13 +903,13 @@
         <v>3.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -843,13 +917,13 @@
         <v>3.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -857,13 +931,13 @@
         <v>3.0001003E7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -871,13 +945,41 @@
         <v>3.0001004E7</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>3.0001005E7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>3.0001006E7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -908,13 +1010,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -922,19 +1024,19 @@
         <v>4.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -942,19 +1044,19 @@
         <v>4.0001002E7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -962,19 +1064,19 @@
         <v>4.0001003E7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1003,10 +1105,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -1014,13 +1116,13 @@
         <v>5.0001001E7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1">
         <v>0.0</v>
